--- a/data/availability/projects/hassan-allam-properties/park-central-mostakbal-city.xlsx
+++ b/data/availability/projects/hassan-allam-properties/park-central-mostakbal-city.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1259,7 +1259,6 @@
       <c r="G2" t="n">
         <v>81</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1270,7 +1269,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1331,7 +1330,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1377,7 +1376,6 @@
       <c r="G4" t="n">
         <v>105</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1388,7 +1386,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1434,7 +1432,6 @@
       <c r="G5" t="n">
         <v>142</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1445,7 +1442,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1506,7 +1503,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1552,7 +1549,6 @@
       <c r="G7" t="n">
         <v>85</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1563,7 +1559,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1609,7 +1605,6 @@
       <c r="G8" t="n">
         <v>143</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1620,7 +1615,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1666,7 +1661,6 @@
       <c r="G9" t="n">
         <v>171</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1677,7 +1671,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1723,7 +1717,6 @@
       <c r="G10" t="n">
         <v>253</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1734,7 +1727,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1795,7 +1788,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1856,7 +1849,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1917,7 +1910,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1978,7 +1971,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2039,7 +2032,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
